--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/magallanes.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1490,7 +1490,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1233613-3836-CM25</t>
+          <t>1233613-3835-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6518.23</v>
+        <v>26852.35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1233613-3835-CM25</t>
+          <t>1233613-3836-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>26852.35</v>
+        <v>6518.23</v>
       </c>
     </row>
     <row r="20">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>AURA XD SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3267,7 +3267,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1233613-1282-CM26</t>
+          <t>1233613-1281-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1511.28</v>
+        <v>25773.02</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1233613-1281-CM26</t>
+          <t>1233613-1282-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>25773.02</v>
+        <v>1511.28</v>
       </c>
     </row>
     <row r="49">
@@ -3450,7 +3450,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5394-369-CM26</t>
+          <t>5394-370-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3505,13 +3505,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2272.9</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5394-370-CM26</t>
+          <t>5394-369-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2380</v>
+        <v>2272.9</v>
       </c>
     </row>
     <row r="52">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4303,6 +4303,250 @@
       </c>
       <c r="M63" s="2" t="n">
         <v>27006.51</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1470-41-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>60.511.124-6</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1536-202-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>60.511.123-8</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>3148.74</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>764-206-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>60.511.120-3</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>3148.74</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2019-64-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>60.511.122-k</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>PRODATA S.A</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>3154.81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/magallanes.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/magallanes.xlsx
@@ -562,7 +562,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1590,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1785,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1976,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2041,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2106,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2171,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2297,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2362,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2427,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2492,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2622,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2687,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2813,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2878,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2943,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3008,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3254,7 +3382,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3315,7 +3447,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3376,7 +3512,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3437,7 +3577,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3620,7 +3764,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3681,7 +3829,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3742,7 +3894,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3803,7 +3959,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3864,7 +4024,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3925,7 +4089,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3986,7 +4154,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4234,7 +4406,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4295,7 +4471,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4356,7 +4536,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4539,7 +4723,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/magallanes.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1542,7 +1542,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1233613-3835-CM25</t>
+          <t>1233613-3836-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>26852.35</v>
+        <v>6518.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1233613-3836-CM25</t>
+          <t>1233613-3835-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6518.23</v>
+        <v>26852.35</v>
       </c>
     </row>
     <row r="20">
@@ -2765,7 +2765,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1609-121-CM26</t>
+          <t>1109692-132-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3519.81</v>
+        <v>522.41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1609-122-CM26</t>
+          <t>3542-123-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2870,26 +2870,22 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>963.9</v>
+        <v>136.73</v>
       </c>
     </row>
     <row r="39">
@@ -2960,7 +2956,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1109692-132-CM26</t>
+          <t>1609-122-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2985,12 +2981,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3000,12 +2996,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3019,13 +3015,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>522.41</v>
+        <v>963.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3542-123-CM26</t>
+          <t>1609-121-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3050,12 +3046,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3065,22 +3061,26 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>136.73</v>
+        <v>3519.81</v>
       </c>
     </row>
     <row r="42">
@@ -3781,7 +3781,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5394-391-CM26</t>
+          <t>5338-380-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1234.02</v>
+        <v>469.55</v>
       </c>
     </row>
     <row r="54">
@@ -3911,7 +3911,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5338-380-CM26</t>
+          <t>5394-391-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3970,13 +3970,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>469.55</v>
+        <v>1234.02</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1233613-1327-CM26</t>
+          <t>1233613-1328-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>16207.44</v>
+        <v>8643.969999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1233613-1328-CM26</t>
+          <t>1233613-1329-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4100,13 +4100,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>8643.969999999999</v>
+        <v>1620.74</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1233613-1329-CM26</t>
+          <t>1233613-1327-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1620.74</v>
+        <v>16207.44</v>
       </c>
     </row>
     <row r="59">
@@ -4553,7 +4553,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1536-202-CM26</t>
+          <t>764-206-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>60.511.120-3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4614,7 +4614,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>764-206-CM26</t>
+          <t>2019-64-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60.511.120-3</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4654,28 +4654,32 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3148.74</v>
+        <v>3154.81</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2019-64-CM26</t>
+          <t>1536-202-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4700,12 +4704,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4715,26 +4719,526 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>3148.74</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1237328-591-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>70.931.900-0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="n">
-        <v>3154.81</v>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>38735.69</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>697-307-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>60.605.000-3</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>4457.54</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1609-362-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>72.229.800-4</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>10695.72</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1237328-606-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>70.931.900-0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>2826.73</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>697-309-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>60.605.000-3</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>1508.3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>697-308-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>60.605.000-3</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>1499.4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1237328-640-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>70.931.900-0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>6850.04</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1237328-652-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>70.931.900-0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>32177.22</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/magallanes.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/magallanes.xlsx
@@ -3801,7 +3801,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
